--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
         <v>2.9</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>2.06</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.06</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.57</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46034.69791666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1977,40 +1977,40 @@
         <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
         <v>2.08</v>
@@ -2019,22 +2019,22 @@
         <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1144,40 +1144,40 @@
         <v>12.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA6" t="n">
         <v>1.65</v>
@@ -1186,22 +1186,22 @@
         <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -2215,34 +2215,34 @@
         <v>2.57</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
         <v>1.52</v>
@@ -2257,22 +2257,22 @@
         <v>1.48</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="N16" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>1.7</v>
@@ -2370,10 +2370,10 @@
         <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>2.7</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1198,7 +1198,7 @@
         <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
         <v>4.65</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1977,10 +1977,10 @@
         <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
         <v>4.16</v>
@@ -1995,10 +1995,10 @@
         <v>2.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2007,10 +2007,10 @@
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA13" t="n">
         <v>2.08</v>
@@ -2019,22 +2019,22 @@
         <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2096,25 +2096,25 @@
         <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
         <v>8.5</v>
@@ -2123,13 +2123,13 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
         <v>2.15</v>
@@ -2138,22 +2138,22 @@
         <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2215,19 +2215,19 @@
         <v>2.57</v>
       </c>
       <c r="O15" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="T15" t="n">
         <v>3.3</v>
@@ -2236,13 +2236,13 @@
         <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
         <v>1.52</v>
@@ -2337,16 +2337,16 @@
         <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.6</v>
+        <v>10.19</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="T16" t="n">
         <v>2.4</v>
@@ -2355,13 +2355,13 @@
         <v>1.51</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>1.22</v>
@@ -2379,7 +2379,7 @@
         <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE16" t="n">
         <v>2.21</v>
@@ -2388,7 +2388,7 @@
         <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
         <v>3.82</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.97</v>
+        <v>3.49</v>
       </c>
       <c r="R14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O15" t="n">
         <v>2.91</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.68</v>
-      </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.49</v>
+        <v>3.97</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -668,64 +668,64 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46034.22916666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46034.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.57</v>
       </c>
       <c r="O13" t="n">
-        <v>2.69</v>
+        <v>3.68</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.16</v>
+        <v>3.49</v>
       </c>
       <c r="R13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>3.68</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.49</v>
+        <v>4.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.88</v>
+        <v>3.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1177,7 +1177,7 @@
         <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
         <v>1.65</v>
@@ -1189,7 +1189,7 @@
         <v>2.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
         <v>2.61</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1626,7 +1626,7 @@
         <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="R10" t="n">
         <v>1.64</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.91</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.68</v>
-      </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.49</v>
+        <v>3.97</v>
       </c>
       <c r="R13" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>3.69</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.97</v>
+        <v>4.11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2337,10 +2337,10 @@
         <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.19</v>
+        <v>9.4</v>
       </c>
       <c r="R16" t="n">
         <v>1.34</v>
@@ -2361,7 +2361,7 @@
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.22</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.51</v>
+        <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>4.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.61</v>
+        <v>1.58</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.65</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.7</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1495,25 +1495,25 @@
         <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="T9" t="n">
         <v>1.97</v>
@@ -1522,7 +1522,7 @@
         <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="W9" t="n">
         <v>1.16</v>
@@ -1531,19 +1531,19 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AB9" t="n">
         <v>2.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
         <v>1.84</v>
@@ -1552,10 +1552,10 @@
         <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
         <v>1.42</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>2.75</v>
@@ -1626,13 +1626,13 @@
         <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.28</v>
+        <v>4.65</v>
       </c>
       <c r="R10" t="n">
         <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
         <v>3.4</v>
@@ -1650,22 +1650,22 @@
         <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE10" t="n">
         <v>2.14</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.53</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="T11" t="n">
         <v>2.03</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.18</v>
+        <v>6.1</v>
       </c>
       <c r="AA11" t="n">
         <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>4.27</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.21</v>
+        <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>3.69</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.82</v>
+        <v>4.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.91</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.69</v>
-      </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="M16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>11.34</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46034.69791666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -671,7 +671,7 @@
         <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
         <v>2.24</v>
@@ -683,16 +683,16 @@
         <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
         <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -701,13 +701,13 @@
         <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>2.92</v>
@@ -716,10 +716,10 @@
         <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG2" t="n">
         <v>1.21</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="M3" t="n">
         <v>3.55</v>
@@ -790,16 +790,16 @@
         <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>2.56</v>
@@ -811,7 +811,7 @@
         <v>6.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -820,7 +820,7 @@
         <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
         <v>1.76</v>
@@ -832,13 +832,13 @@
         <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
         <v>1.9</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>17.16</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>2.27</v>
+        <v>2.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.78</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.21</v>
+        <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.02</v>
+        <v>4.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.3</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>11</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.55</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AB9" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.16</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>2.93</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.65</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>3.82</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Z10" t="n">
-        <v>2.66</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>3.16</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>4.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.27</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.91</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.69</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.97</v>
+        <v>3.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.11</v>
+        <v>4.54</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
@@ -2230,7 +2230,7 @@
         <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
@@ -2248,13 +2248,13 @@
         <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
         <v>3.42</v>
@@ -2263,16 +2263,16 @@
         <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.69</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="M9" t="n">
-        <v>2.93</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA10" t="n">
         <v>2.55</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AB10" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.84</v>
+        <v>1.13</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.16</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.27</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>4.27</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>2.75</v>
@@ -2016,7 +2016,7 @@
         <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
         <v>3.82</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>2.6</v>
@@ -2251,10 +2251,10 @@
         <v>3.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>3.42</v>
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.73</v>
+        <v>2.57</v>
       </c>
       <c r="O17" t="n">
         <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
         <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
@@ -2483,34 +2483,34 @@
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.52</v>
+        <v>3.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>17.16</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="N9" t="n">
-        <v>2.69</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="M10" t="n">
-        <v>2.93</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>4.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.27</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.82</v>
+        <v>4.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.6</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>4.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.88</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,61 +2206,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.54</v>
+        <v>4.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
         <v>1.82</v>
@@ -2269,10 +2269,10 @@
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -671,10 +671,10 @@
         <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
@@ -686,46 +686,46 @@
         <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="V2" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG2" t="n">
         <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46034.22916666666</v>
@@ -781,10 +781,10 @@
         <v>3.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O3" t="n">
         <v>4.6</v>
@@ -796,7 +796,7 @@
         <v>2.31</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
         <v>2.92</v>
@@ -805,7 +805,7 @@
         <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
         <v>6.2</v>
@@ -817,34 +817,34 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
         <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
         <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46034.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.78</v>
+        <v>9.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>2.48</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.42</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>4.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.9</v>
+        <v>4.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH7" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.65</v>
+        <v>3.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>3.88</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.58</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.66</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.55</v>
+        <v>1.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>2.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>3.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.27</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>4.27</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.7</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.45</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.54</v>
-      </c>
       <c r="R14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.45</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.75</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="N16" t="n">
-        <v>11.34</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>1.67</v>
@@ -2343,22 +2343,22 @@
         <v>9.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
         <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V16" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
@@ -2367,19 +2367,19 @@
         <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA16" t="n">
         <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
         <v>2.23</v>
@@ -2388,10 +2388,10 @@
         <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.8</v>
+        <v>4.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46034.69791666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.9</v>
+        <v>4.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.7</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.01</v>
+        <v>4.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>3.88</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.16</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.28</v>
+        <v>3.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>3.88</v>
       </c>
       <c r="T10" t="n">
-        <v>3.72</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="W10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.01</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>1.31</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>2.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>3.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
         <v>2.38</v>
@@ -1745,10 +1745,10 @@
         <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
@@ -1757,7 +1757,7 @@
         <v>2.03</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
         <v>4.1</v>
@@ -1769,10 +1769,10 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.4</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>2.01</v>
@@ -1867,7 +1867,7 @@
         <v>4.27</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
@@ -1897,10 +1897,10 @@
         <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AD12" t="n">
         <v>1.76</v>
@@ -1912,7 +1912,7 @@
         <v>2.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
         <v>2.02</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.75</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.27</v>
+        <v>3.87</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2471,13 +2471,13 @@
         <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
         <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -671,58 +671,58 @@
         <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
         <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.88</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V2" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
         <v>1.12</v>
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
         <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
         <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="Q3" t="n">
         <v>2.31</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
         <v>6.2</v>
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
         <v>3.58</v>
@@ -835,13 +835,13 @@
         <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
         <v>2.03</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="n">
         <v>1.16</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.7</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -906,64 +906,64 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46034.50694444445</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.84</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>3.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.3</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,40 +1730,40 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.47</v>
+        <v>4.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,31 +1772,31 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,40 +1849,40 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.27</v>
+        <v>3.47</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U12" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,31 +1891,31 @@
         <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>4.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -906,28 +906,28 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.08</v>
+        <v>4.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.74</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.89</v>
       </c>
       <c r="U4" t="n">
         <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -936,34 +936,34 @@
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.37</v>
+        <v>3.47</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46034.50694444445</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.9</v>
+        <v>4.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.7</v>
+        <v>2.16</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.08</v>
       </c>
       <c r="O9" t="n">
         <v>2.75</v>
@@ -1516,49 +1516,49 @@
         <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
         <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.45</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.27</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.42</v>
+        <v>4.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.75</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O15" t="n">
         <v>2.91</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.28</v>
       </c>
-      <c r="V15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2328,19 +2328,19 @@
         <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P16" t="n">
         <v>2.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.5</v>
+        <v>6.95</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
@@ -2355,7 +2355,7 @@
         <v>1.54</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
@@ -2373,7 +2373,7 @@
         <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC16" t="n">
         <v>2.75</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="O17" t="n">
         <v>3.1</v>
@@ -2462,16 +2462,16 @@
         <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
         <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
         <v>6.5</v>
@@ -2486,13 +2486,13 @@
         <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
         <v>3.75</v>
@@ -2501,16 +2501,16 @@
         <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -671,61 +671,61 @@
         <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.79</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AF2" t="n">
         <v>1.82</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46034.22916666666</v>
@@ -781,28 +781,28 @@
         <v>3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O3" t="n">
         <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
         <v>1.41</v>
@@ -820,7 +820,7 @@
         <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
         <v>1.76</v>
@@ -829,7 +829,7 @@
         <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="AD3" t="n">
         <v>1.33</v>
@@ -838,7 +838,7 @@
         <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
         <v>1.9</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.74</v>
+        <v>9.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.16</v>
+        <v>4.65</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>4.08</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.75</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.28</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>3.76</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>10.7</v>
+        <v>3.85</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.66</v>
+        <v>6.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>1.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>3.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>4.08</v>
       </c>
       <c r="O10" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>3.76</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>3.85</v>
+        <v>10.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>2.66</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.88</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>2.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.49</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="O11" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="P11" t="n">
         <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -1757,10 +1757,10 @@
         <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.16</v>
@@ -1778,7 +1778,7 @@
         <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="AC11" t="n">
         <v>2.04</v>
@@ -1793,10 +1793,10 @@
         <v>2.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
         <v>3.78</v>
@@ -1861,13 +1861,13 @@
         <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
         <v>3.68</v>
@@ -1876,19 +1876,19 @@
         <v>2.03</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
         <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
         <v>5.6</v>
@@ -1900,10 +1900,10 @@
         <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>1.36</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.97</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.88</v>
+        <v>3.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.2</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>4.52</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.81</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="M17" t="n">
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
         <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
         <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
         <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
         <v>3.75</v>
@@ -2501,13 +2501,13 @@
         <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
         <v>1.98</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
         <v>1.49</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.74</v>
+        <v>9.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
         <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>4.65</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="M8" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>4.08</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="N10" t="n">
-        <v>4.08</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="N11" t="n">
-        <v>3.98</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.22</v>
+        <v>3.42</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -1754,49 +1754,49 @@
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
         <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>3.98</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.42</v>
+        <v>4.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1873,49 +1873,49 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC12" t="n">
         <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.5</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>3.08</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.02</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.91</v>
+        <v>3.64</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.87</v>
+        <v>3.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.06</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>4.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.08</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.75</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.28</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>3.76</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>10.7</v>
+        <v>3.85</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.66</v>
+        <v>6.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>1.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>3.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>3.76</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>3.85</v>
+        <v>10.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>2.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.32</v>
+        <v>2.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.88</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>2.91</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.15</v>
+        <v>3.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.87</v>
+        <v>4.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O15" t="n">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="R15" t="n">
         <v>1.53</v>
@@ -2245,19 +2245,19 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
         <v>2.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB15" t="n">
         <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="AD15" t="n">
         <v>1.16</v>
@@ -2272,7 +2272,7 @@
         <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>1.68</v>
@@ -2340,25 +2340,25 @@
         <v>2.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
         <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
         <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
@@ -2370,16 +2370,16 @@
         <v>4.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
         <v>2.23</v>
@@ -2388,10 +2388,10 @@
         <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.02</v>
+        <v>3.8</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46034.69791666666</v>
@@ -2444,25 +2444,25 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
         <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
         <v>2.67</v>
@@ -2471,7 +2471,7 @@
         <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
         <v>7</v>
@@ -2495,22 +2495,22 @@
         <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.75</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>3.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>2.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>3.98</v>
       </c>
       <c r="O11" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.42</v>
+        <v>4.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -1754,49 +1754,49 @@
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC11" t="n">
         <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="N12" t="n">
-        <v>3.98</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.22</v>
+        <v>3.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1873,49 +1873,49 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
         <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3.07</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.87</v>
+        <v>4.54</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.15</v>
+        <v>3.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -671,28 +671,28 @@
         <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -704,28 +704,28 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46034.22916666666</v>
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="M3" t="n">
         <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
         <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
         <v>6.2</v>
@@ -817,31 +817,31 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
         <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AD3" t="n">
         <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
         <v>1.16</v>
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.57</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
         <v>2.78</v>
@@ -927,43 +927,43 @@
         <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
         <v>3.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46034.50694444445</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>4.03</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
         <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.74</v>
+        <v>4.55</v>
       </c>
       <c r="R5" t="n">
         <v>1.28</v>
@@ -1040,7 +1040,7 @@
         <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
@@ -1055,34 +1055,34 @@
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.3</v>
+        <v>4.52</v>
       </c>
       <c r="AA5" t="n">
         <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>3.76</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>3.85</v>
+        <v>10.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.32</v>
+        <v>2.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.88</v>
+        <v>4.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.49</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
         <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>10.7</v>
+        <v>3.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>2.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="M13" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.54</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.19</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.87</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
         <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.82</v>
+        <v>4.54</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.43</v>
+        <v>3.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.38</v>
+        <v>4.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.3</v>
       </c>
-      <c r="V15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.54</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="N16" t="n">
         <v>10</v>
@@ -2346,34 +2346,34 @@
         <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
         <v>4.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>2.75</v>
@@ -2382,16 +2382,16 @@
         <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.8</v>
+        <v>4.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46034.69791666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>4.03</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.55</v>
+        <v>9.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.52</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.05</v>
+        <v>4.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>4.03</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.9</v>
+        <v>4.55</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>2.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.7</v>
+        <v>2.05</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>10.7</v>
+        <v>3.85</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.46</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>2.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.22</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -1754,16 +1754,16 @@
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,31 +1772,31 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>3.78</v>
+        <v>3.96</v>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.42</v>
+        <v>4.17</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1873,49 +1873,49 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC12" t="n">
         <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>3.77</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>3.77</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC15" t="n">
         <v>4.54</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.42</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
         <v>3.25</v>
@@ -2471,7 +2471,7 @@
         <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
         <v>7</v>
@@ -2486,13 +2486,13 @@
         <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
         <v>3.48</v>
@@ -2501,7 +2501,7 @@
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
         <v>1.95</v>
@@ -2510,7 +2510,7 @@
         <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O2" t="n">
         <v>4.3</v>
@@ -680,7 +680,7 @@
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
         <v>2.79</v>
@@ -689,10 +689,10 @@
         <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -704,7 +704,7 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
@@ -784,16 +784,16 @@
         <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O3" t="n">
         <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
@@ -802,10 +802,10 @@
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
         <v>6.2</v>
@@ -826,7 +826,7 @@
         <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>2.99</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.9</v>
+        <v>4.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.43</v>
+        <v>2.21</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>4.03</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1144,40 +1144,40 @@
         <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA6" t="n">
         <v>2.15</v>
@@ -1186,22 +1186,22 @@
         <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1287,7 +1287,7 @@
         <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
@@ -1296,7 +1296,7 @@
         <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
         <v>1.65</v>
@@ -1314,7 +1314,7 @@
         <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG7" t="n">
         <v>1.09</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>10.7</v>
+        <v>3.85</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>2.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.19</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.17</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.82</v>
+        <v>4.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>3.77</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.54</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
         <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.97</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="AA15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2340,10 +2340,10 @@
         <v>2.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
         <v>3.28</v>
@@ -2352,22 +2352,22 @@
         <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V16" t="n">
         <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
         <v>1.7</v>
@@ -2382,10 +2382,10 @@
         <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
         <v>1.16</v>
@@ -2450,7 +2450,7 @@
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
         <v>3.25</v>
@@ -2495,16 +2495,16 @@
         <v>1.76</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>2.74</v>
@@ -939,13 +939,13 @@
         <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
         <v>3.14</v>
@@ -954,16 +954,16 @@
         <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46034.50694444445</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>4.02</v>
       </c>
       <c r="N5" t="n">
         <v>3.85</v>
@@ -1070,7 +1070,7 @@
         <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
         <v>1.58</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>10.7</v>
+        <v>3.85</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>1.32</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.12</v>
+        <v>1.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1733,13 +1733,13 @@
         <v>2.11</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="O11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="P11" t="n">
         <v>2.62</v>
@@ -1760,10 +1760,10 @@
         <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>5.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
         <v>2.7</v>
@@ -1793,7 +1793,7 @@
         <v>2.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
         <v>1.68</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="P12" t="n">
         <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1876,13 +1876,13 @@
         <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,31 +1891,31 @@
         <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AC12" t="n">
         <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.37</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="N15" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.54</v>
+        <v>3.38</v>
       </c>
       <c r="R15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="M16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
         <v>1.68</v>
@@ -2346,40 +2346,40 @@
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
         <v>1.54</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
         <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
         <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
         <v>2.32</v>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="M17" t="n">
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
         <v>2.05</v>
@@ -2462,13 +2462,13 @@
         <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
         <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
         <v>1.37</v>
@@ -2510,7 +2510,7 @@
         <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>
@@ -2566,70 +2566,70 @@
         <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA18" t="n">
         <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46034.79166666666</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O2" t="n">
         <v>4.3</v>
@@ -680,16 +680,16 @@
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
         <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -701,28 +701,28 @@
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH2" t="n">
         <v>1.18</v>
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
         <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
@@ -802,7 +802,7 @@
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
         <v>1.41</v>
@@ -826,22 +826,22 @@
         <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
         <v>2.99</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="n">
         <v>1.16</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="M5" t="n">
-        <v>4.02</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.72</v>
+        <v>3.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.52</v>
+        <v>2.83</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
-        <v>2.98</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.93</v>
+        <v>9.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>7.9</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.83</v>
+        <v>4.19</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC6" t="n">
-        <v>3.92</v>
+        <v>2.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>4.02</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.9</v>
+        <v>4.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>4.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>3.92</v>
+        <v>2.37</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>3.85</v>
+        <v>10.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>1.46</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.45</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.32</v>
+        <v>2.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.87</v>
+        <v>4.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.31</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.98</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.5</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
         <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.37</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.22</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>12</v>
       </c>
       <c r="O5" t="n">
-        <v>2.78</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.9</v>
+        <v>9.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="V5" t="n">
-        <v>7.9</v>
+        <v>5.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.83</v>
+        <v>4.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>2.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>2.78</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.19</v>
+        <v>2.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.67</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.7</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.02</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.61</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.37</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2572,64 +2572,64 @@
         <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>6.49</v>
+        <v>6.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
         <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46034.79166666666</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>4.02</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>4.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.83</v>
+        <v>4.52</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>4.02</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="P7" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.72</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.52</v>
+        <v>2.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="M9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF9" t="n">
         <v>3.1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.13</v>
+        <v>5.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3.92</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>3.64</v>
       </c>
       <c r="U10" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>3.85</v>
+        <v>10.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.45</v>
+        <v>2.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.32</v>
+        <v>2.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>4.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.31</v>
+        <v>2.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
         <v>2.54</v>
@@ -2349,37 +2349,37 @@
         <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
         <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
         <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
         <v>2.32</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>6.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
         <v>1.44</v>
@@ -2608,10 +2608,10 @@
         <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AC18" t="n">
         <v>2.44</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
         <v>9.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
         <v>1.48</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
         <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG5" t="n">
         <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1254,28 +1254,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="T7" t="n">
         <v>3.1</v>
@@ -1287,10 +1287,10 @@
         <v>7.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
         <v>1.33</v>
@@ -1299,10 +1299,10 @@
         <v>2.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>4.2</v>
@@ -1311,16 +1311,16 @@
         <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>4.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -1754,16 +1754,16 @@
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,31 +1772,31 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AG11" t="n">
         <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="O12" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.22</v>
+        <v>3.49</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1873,16 +1873,16 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,31 +1891,31 @@
         <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AG12" t="n">
         <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>2.57</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.02</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.61</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.37</v>
+        <v>3.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
         <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.06</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>4.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="M4" t="n">
-        <v>3.44</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>3.72</v>
+        <v>4.02</v>
       </c>
       <c r="O4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="P4" t="n">
         <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.95</v>
+        <v>4.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF4" t="n">
         <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46034.50694444445</v>
@@ -1025,10 +1025,10 @@
         <v>12.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="Q5" t="n">
         <v>9.9</v>
@@ -1043,7 +1043,7 @@
         <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
         <v>6</v>
@@ -1067,22 +1067,22 @@
         <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AG5" t="n">
         <v>1.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>2.2</v>
@@ -1150,7 +1150,7 @@
         <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.72</v>
+        <v>3.87</v>
       </c>
       <c r="R6" t="n">
         <v>1.28</v>
@@ -1159,10 +1159,10 @@
         <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
         <v>5.3</v>
@@ -1174,7 +1174,7 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
         <v>4.52</v>
@@ -1183,25 +1183,25 @@
         <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1263,19 +1263,19 @@
         <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="P7" t="n">
         <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.93</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
         <v>3.1</v>
@@ -1287,16 +1287,16 @@
         <v>7.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AA7" t="n">
         <v>2.15</v>
@@ -1317,7 +1317,7 @@
         <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
         <v>1.57</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.05</v>
+        <v>3.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="T10" t="n">
-        <v>3.64</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>10.7</v>
+        <v>4.05</v>
       </c>
       <c r="W10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.01</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.47</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.66</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>2.11</v>
       </c>
       <c r="M11" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="O11" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.22</v>
+        <v>3.49</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -1754,16 +1754,16 @@
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,31 +1772,31 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AG11" t="n">
         <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.49</v>
+        <v>4.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1873,16 +1873,16 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,31 +1891,31 @@
         <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AG12" t="n">
         <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1989,7 +1989,7 @@
         <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
         <v>2.75</v>
@@ -2001,13 +2001,13 @@
         <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
         <v>2.97</v>
@@ -2031,10 +2031,10 @@
         <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.19</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.82</v>
+        <v>4.68</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.8</v>
+        <v>2.19</v>
       </c>
       <c r="M15" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.38</v>
+        <v>4.03</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
         <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.37</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2328,10 +2328,10 @@
         <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="N16" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>1.67</v>
@@ -2340,52 +2340,52 @@
         <v>2.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.5</v>
+        <v>7.34</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
         <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
         <v>1.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
         <v>1.16</v>
@@ -2572,25 +2572,25 @@
         <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>6.1</v>
+        <v>5.99</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
         <v>5.1</v>
@@ -2602,10 +2602,10 @@
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA18" t="n">
         <v>1.8</v>
@@ -2614,22 +2614,22 @@
         <v>1.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46034.79166666666</v>
@@ -2691,40 +2691,40 @@
         <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
         <v>1.73</v>
@@ -2733,22 +2733,22 @@
         <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46034.89583333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.55</v>
+        <v>4.73</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="N2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="O2" t="n">
         <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -683,13 +683,13 @@
         <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V2" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -698,31 +698,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.99</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
         <v>1.18</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="M3" t="n">
         <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
         <v>4.7</v>
@@ -796,13 +796,13 @@
         <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
         <v>1.41</v>
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
         <v>3.58</v>
@@ -829,22 +829,22 @@
         <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
         <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46034.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>3.87</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.9</v>
+        <v>3.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.1</v>
+        <v>4.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.61</v>
+        <v>1.66</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.45</v>
+        <v>2.19</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.8</v>
+        <v>2.01</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.52</v>
+        <v>2.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.96</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>9.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>3.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.92</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>3.64</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>4.05</v>
+        <v>10.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>2.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.35</v>
+        <v>2.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1730,19 +1730,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
         <v>3.49</v>
@@ -1754,16 +1754,16 @@
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>4.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,19 +1772,19 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB11" t="n">
         <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE11" t="n">
         <v>1.36</v>
@@ -1793,7 +1793,7 @@
         <v>2.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
         <v>1.68</v>
@@ -1858,7 +1858,7 @@
         <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="P12" t="n">
         <v>2.41</v>
@@ -1873,16 +1873,16 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1894,22 +1894,22 @@
         <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
         <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AG12" t="n">
         <v>1.21</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.91</v>
       </c>
       <c r="M13" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>2.57</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.42</v>
+        <v>4.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2.97</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="AA14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2444,25 +2444,25 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="M17" t="n">
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
         <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
         <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
         <v>2.67</v>
@@ -2495,22 +2495,22 @@
         <v>1.76</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="AD17" t="n">
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.07</v>
+        <v>3.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>4.7</v>
+        <v>4.44</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.92</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AF3" t="n">
         <v>2.03</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46034.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.52</v>
+        <v>2.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.87</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.96</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.86</v>
+        <v>4.52</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="N9" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.49</v>
+        <v>4.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -1754,16 +1754,16 @@
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,31 +1772,31 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>2.06</v>
       </c>
       <c r="M12" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.22</v>
+        <v>3.49</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1873,16 +1873,16 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,31 +1891,31 @@
         <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P14" t="n">
         <v>1.95</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q14" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>3.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.03</v>
+        <v>4.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -764,17 +764,17 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -1025,25 +1025,25 @@
         <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
         <v>7.9</v>
@@ -1055,10 +1055,10 @@
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AA5" t="n">
         <v>2.15</v>
@@ -1067,22 +1067,22 @@
         <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.2</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.27</v>
-      </c>
       <c r="Q6" t="n">
-        <v>3.87</v>
+        <v>4.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>5.85</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.52</v>
+        <v>3.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
         <v>1.66</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1266,25 +1266,25 @@
         <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
         <v>9.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
         <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="W7" t="n">
         <v>1.14</v>
@@ -1296,7 +1296,7 @@
         <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
         <v>1.65</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
         <v>2.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG7" t="n">
         <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1620,31 +1620,31 @@
         <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1.06</v>
@@ -1662,13 +1662,13 @@
         <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AD10" t="n">
         <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AF10" t="n">
         <v>1.66</v>
@@ -1677,7 +1677,7 @@
         <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="P11" t="n">
         <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.16</v>
@@ -1781,7 +1781,7 @@
         <v>2.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AD11" t="n">
         <v>1.76</v>
@@ -1796,7 +1796,7 @@
         <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
         <v>2.39</v>
@@ -1873,10 +1873,10 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
         <v>4.2</v>
@@ -1891,19 +1891,19 @@
         <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
         <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>1.36</v>
@@ -1977,22 +1977,22 @@
         <v>2.57</v>
       </c>
       <c r="O13" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.35</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
       </c>
       <c r="U13" t="n">
         <v>1.28</v>
@@ -2004,7 +2004,7 @@
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
         <v>1.52</v>
@@ -2019,22 +2019,22 @@
         <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.68</v>
+        <v>4.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
         <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>2.91</v>
@@ -2132,7 +2132,7 @@
         <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
         <v>1.63</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="O15" t="n">
         <v>2.68</v>
@@ -2251,10 +2251,10 @@
         <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>3.4</v>
@@ -2334,22 +2334,22 @@
         <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P16" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.34</v>
+        <v>7.43</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
         <v>1.53</v>
@@ -2358,7 +2358,7 @@
         <v>5.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
@@ -2376,10 +2376,10 @@
         <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
         <v>2.21</v>
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P17" t="n">
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
         <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="U17" t="n">
         <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
         <v>1.06</v>
@@ -2486,7 +2486,7 @@
         <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="AA17" t="n">
         <v>2.09</v>
@@ -2504,13 +2504,13 @@
         <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG17" t="n">
         <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>
@@ -2563,70 +2563,70 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.57</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
         <v>5.99</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
         <v>1.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="T18" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
         <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH18" t="n">
         <v>1.06</v>
@@ -2691,13 +2691,13 @@
         <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="R19" t="n">
         <v>1.3</v>
@@ -2706,10 +2706,10 @@
         <v>3.04</v>
       </c>
       <c r="T19" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
         <v>5.7</v>
@@ -2733,22 +2733,22 @@
         <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46034.89583333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.2</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.16</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>6.25</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.94</v>
+        <v>11.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.07</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.96</v>
+        <v>4.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>3.87</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5</v>
+        <v>4.18</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.9</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AD7" t="n">
         <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.58</v>
+        <v>2.93</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.35</v>
+        <v>4.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>3.92</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>3.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>4.05</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.87</v>
+        <v>4.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.57</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>3.44</v>
+        <v>2.68</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>4.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.73</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.95</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>3.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
         <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.31</v>
+        <v>2.82</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -880,90 +880,90 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="N4" t="n">
-        <v>4.02</v>
+        <v>4.42</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.57</v>
+        <v>3.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46034.50694444445</v>
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,16 +1109,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
-        <v>6.25</v>
+        <v>3.87</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>4.18</v>
       </c>
       <c r="O6" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.75</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.55</v>
+        <v>3.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>3.87</v>
+        <v>6.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.18</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE7" t="n">
         <v>2.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="AF7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.07</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.95</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>3.08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.72</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.25</v>
       </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.83</v>
+        <v>4.19</v>
       </c>
       <c r="O9" t="n">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.92</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>4.05</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>2.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>2.61</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>4.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.9</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="M10" t="n">
-        <v>3.58</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>2.86</v>
       </c>
       <c r="O11" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.27</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
@@ -1873,16 +1873,16 @@
         <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
         <v>4.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,31 +1891,31 @@
         <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46034.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.45</v>
+        <v>3.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.43</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
         <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>5.65</v>
+        <v>5.45</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46034.69791666666</v>
@@ -2566,70 +2566,70 @@
         <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.43</v>
       </c>
-      <c r="O18" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
         <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46034.79166666666</v>
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V19" t="n">
         <v>5.7</v>
@@ -2718,37 +2718,37 @@
         <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
         <v>2.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46034.89583333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,23 +1109,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87</v>
+        <v>6.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.18</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2.2</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="AF6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.07</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>6.25</v>
+        <v>3.87</v>
       </c>
       <c r="N7" t="n">
-        <v>11</v>
+        <v>4.18</v>
       </c>
       <c r="O7" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.75</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.55</v>
+        <v>3.94</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1347,22 +1347,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
-        <v>2.98</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="S8" t="n">
-        <v>3.08</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.05</v>
+        <v>7.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.32</v>
+        <v>3.36</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,25 +1466,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>4.19</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.25</v>
       </c>
-      <c r="V9" t="n">
-        <v>8</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.13</v>
       </c>
-      <c r="S10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.27</v>
+        <v>2.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.36</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46034.60416666666</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1964,65 +1964,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.9</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
         <v>1.83</v>
@@ -2031,10 +2031,10 @@
         <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2061,87 +2061,87 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
         <v>1.83</v>
@@ -2150,10 +2150,10 @@
         <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46034.6875</v>
@@ -2189,20 +2189,20 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2308,20 +2308,20 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,19 +2418,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.55</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.25</v>
       </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>2.53</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.54</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46034.70833333334</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,19 +2537,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2559,80 +2559,80 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>2.55</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>2.82</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>3.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46034.79166666666</v>
+        <v>46034.70833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.25</v>
       </c>
-      <c r="N19" t="n">
-        <v>4</v>
-      </c>
       <c r="O19" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="P19" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
         <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
         <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46034.89583333334</v>

--- a/jogos_2026-01-12.xlsx
+++ b/jogos_2026-01-12.xlsx
@@ -990,16 +990,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>6.25</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>11.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="V5" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.66</v>
+        <v>4.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.23</v>
+        <v>1.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.47</v>
+        <v>2.48</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.49</v>
+        <v>4.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1109,16 +1109,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>6.25</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.54</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.75</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>2.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.55</v>
+        <v>2.66</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.59</v>
+        <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.48</v>
+        <v>4.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.7</v>
+        <v>1.49</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46034.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,25 +1942,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q13" t="n">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="T13" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.13</v>
+        <v>2.49</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46034.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,99 +2180,99 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>2.97</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46034.6875</v>
